--- a/RaidenDemo/文档/配置表/EffectResource.xlsx
+++ b/RaidenDemo/文档/配置表/EffectResource.xlsx
@@ -2,7 +2,7 @@
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <x:workbook xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <x:sheets>
-    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Rbdb3584dafe34642"/>
+    <x:sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Sheet1" sheetId="1" r:id="Raeccdbfa5d874584"/>
   </x:sheets>
 </x:workbook>
 </file>
@@ -279,7 +279,7 @@
       <x:name val="Carlito"/>
     </x:font>
   </x:fonts>
-  <x:fills count="39">
+  <x:fills count="40">
     <x:fill>
       <x:patternFill patternType="none"/>
     </x:fill>
@@ -454,6 +454,11 @@
     <x:fill>
       <x:patternFill patternType="solid">
         <x:fgColor theme="9" tint="0.39998"/>
+      </x:patternFill>
+    </x:fill>
+    <x:fill>
+      <x:patternFill patternType="solid">
+        <x:fgColor rgb="FFFFFFFF"/>
       </x:patternFill>
     </x:fill>
     <x:fill>
@@ -718,7 +723,7 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </x:cellStyleXfs>
-  <x:cellXfs count="18">
+  <x:cellXfs count="24">
     <x:xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="49"/>
     <x:xf numFmtId="0" fontId="1" fillId="2" borderId="1" xfId="49" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center"/>
@@ -760,6 +765,20 @@
     </x:xf>
     <x:xf numFmtId="0" fontId="3" fillId="38" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <x:alignment horizontal="center" vertical="center" wrapText="0"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="0" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="39" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
+    </x:xf>
+    <x:xf numFmtId="0" fontId="3" fillId="4" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <x:alignment horizontal="center" vertical="center"/>
     </x:xf>
   </x:cellXfs>
   <x:cellStyles count="50">
@@ -1565,16 +1584,37 @@
         <x:v>bossBorn_1</x:v>
       </x:c>
     </x:row>
+    <x:row r="21">
+      <x:c r="A21" s="23"/>
+      <x:c r="B21" s="23" t="n">
+        <x:v>12001</x:v>
+      </x:c>
+      <x:c r="C21" s="23" t="str">
+        <x:v>stage_item_reward_frame</x:v>
+      </x:c>
+      <x:c r="D21" s="23" t="str">
+        <x:v>关卡奖励道具通用循环特效</x:v>
+      </x:c>
+      <x:c r="E21" s="23" t="str">
+        <x:v>其他</x:v>
+      </x:c>
+      <x:c r="F21" s="23" t="str">
+        <x:v>reward_frame</x:v>
+      </x:c>
+    </x:row>
   </x:sheetData>
-  <x:dataValidations count="2">
+  <x:dataValidations count="3">
     <x:dataValidation type="list" sqref="E4:E199">
       <x:formula1>"子弹命中特效,飞机爆炸特效"</x:formula1>
     </x:dataValidation>
     <x:dataValidation type="list" sqref="E18:E19">
       <x:formula1>"子弹命中特效,飞机爆炸特效,其他"</x:formula1>
     </x:dataValidation>
+    <x:dataValidation type="list" sqref="E4:E100">
+      <x:formula1>"子弹命中特效,飞机爆炸特效,子弹发射特效,其他"</x:formula1>
+    </x:dataValidation>
   </x:dataValidations>
   <x:pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="Rf5b38e19b61a4b9c"/>
+  <x:legacyDrawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="R12cad2a53daf4f68"/>
 </x:worksheet>
 </file>
--- a/RaidenDemo/文档/配置表/EffectResource.xlsx
+++ b/RaidenDemo/文档/配置表/EffectResource.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="337" uniqueCount="181">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="184">
   <si>
     <t>##var</t>
   </si>
@@ -126,7 +126,7 @@
     <t>EffectType</t>
   </si>
   <si>
-    <t>bullet_shoot_common</t>
+    <t>shootFire_common</t>
   </si>
   <si>
     <t>所有子弹通用发射特效</t>
@@ -135,9 +135,6 @@
     <t>子弹发射</t>
   </si>
   <si>
-    <t>shoot_common</t>
-  </si>
-  <si>
     <t>shootFire_1001</t>
   </si>
   <si>
@@ -285,15 +282,21 @@
     <t>bullet_ball_2007</t>
   </si>
   <si>
+    <t>hit_common</t>
+  </si>
+  <si>
+    <t>子弹命中公共特效</t>
+  </si>
+  <si>
+    <t>子弹命中</t>
+  </si>
+  <si>
     <t>hit_1</t>
   </si>
   <si>
     <t>刺闪爆炸-红黑</t>
   </si>
   <si>
-    <t>子弹命中</t>
-  </si>
-  <si>
     <t>hit_2</t>
   </si>
   <si>
@@ -360,6 +363,12 @@
     <t>电磁爆-紫色</t>
   </si>
   <si>
+    <t>hit_13</t>
+  </si>
+  <si>
+    <t>刺闪-红色2</t>
+  </si>
+  <si>
     <t>explosion_small_1</t>
   </si>
   <si>
@@ -609,7 +618,7 @@
     <t>circle_8</t>
   </si>
   <si>
-    <t>关卡道具环绕_青色消融</t>
+    <t>关卡道具触发_青色消融</t>
   </si>
   <si>
     <t>dust_01</t>
@@ -1819,7 +1828,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F83"/>
+  <dimension ref="A1:F85"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
@@ -1904,7 +1913,7 @@
         <v>17</v>
       </c>
       <c r="F4" s="3" t="s">
-        <v>18</v>
+        <v>15</v>
       </c>
     </row>
     <row r="5" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -1913,16 +1922,16 @@
         <v>2</v>
       </c>
       <c r="C5" s="3" t="s">
+        <v>18</v>
+      </c>
+      <c r="D5" s="3" t="s">
         <v>19</v>
-      </c>
-      <c r="D5" s="3" t="s">
-        <v>20</v>
       </c>
       <c r="E5" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F5" s="3" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
     </row>
     <row r="6" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -1931,16 +1940,16 @@
         <v>3</v>
       </c>
       <c r="C6" s="3" t="s">
+        <v>20</v>
+      </c>
+      <c r="D6" s="3" t="s">
         <v>21</v>
-      </c>
-      <c r="D6" s="3" t="s">
-        <v>22</v>
       </c>
       <c r="E6" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F6" s="3" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
     </row>
     <row r="7" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -1949,16 +1958,16 @@
         <v>4</v>
       </c>
       <c r="C7" s="3" t="s">
+        <v>22</v>
+      </c>
+      <c r="D7" s="3" t="s">
         <v>23</v>
-      </c>
-      <c r="D7" s="3" t="s">
-        <v>24</v>
       </c>
       <c r="E7" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F7" s="3" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
     </row>
     <row r="8" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -1967,16 +1976,16 @@
         <v>5</v>
       </c>
       <c r="C8" s="3" t="s">
+        <v>24</v>
+      </c>
+      <c r="D8" s="3" t="s">
         <v>25</v>
-      </c>
-      <c r="D8" s="3" t="s">
-        <v>26</v>
       </c>
       <c r="E8" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F8" s="3" t="s">
-        <v>25</v>
+        <v>24</v>
       </c>
     </row>
     <row r="9" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -1985,16 +1994,16 @@
         <v>6</v>
       </c>
       <c r="C9" s="3" t="s">
+        <v>26</v>
+      </c>
+      <c r="D9" s="3" t="s">
         <v>27</v>
-      </c>
-      <c r="D9" s="3" t="s">
-        <v>28</v>
       </c>
       <c r="E9" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F9" s="3" t="s">
-        <v>27</v>
+        <v>26</v>
       </c>
     </row>
     <row r="10" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -2003,16 +2012,16 @@
         <v>7</v>
       </c>
       <c r="C10" s="3" t="s">
+        <v>28</v>
+      </c>
+      <c r="D10" s="3" t="s">
         <v>29</v>
-      </c>
-      <c r="D10" s="3" t="s">
-        <v>30</v>
       </c>
       <c r="E10" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F10" s="3" t="s">
-        <v>29</v>
+        <v>28</v>
       </c>
     </row>
     <row r="11" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -2021,16 +2030,16 @@
         <v>8</v>
       </c>
       <c r="C11" s="3" t="s">
+        <v>30</v>
+      </c>
+      <c r="D11" s="3" t="s">
         <v>31</v>
-      </c>
-      <c r="D11" s="3" t="s">
-        <v>32</v>
       </c>
       <c r="E11" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F11" s="3" t="s">
-        <v>31</v>
+        <v>30</v>
       </c>
     </row>
     <row r="12" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -2039,16 +2048,16 @@
         <v>9</v>
       </c>
       <c r="C12" s="3" t="s">
+        <v>32</v>
+      </c>
+      <c r="D12" s="3" t="s">
         <v>33</v>
-      </c>
-      <c r="D12" s="3" t="s">
-        <v>34</v>
       </c>
       <c r="E12" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F12" s="3" t="s">
-        <v>33</v>
+        <v>32</v>
       </c>
     </row>
     <row r="13" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -2057,16 +2066,16 @@
         <v>10</v>
       </c>
       <c r="C13" s="3" t="s">
+        <v>34</v>
+      </c>
+      <c r="D13" s="3" t="s">
         <v>35</v>
-      </c>
-      <c r="D13" s="3" t="s">
-        <v>36</v>
       </c>
       <c r="E13" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F13" s="3" t="s">
-        <v>35</v>
+        <v>34</v>
       </c>
     </row>
     <row r="14" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
@@ -2075,16 +2084,16 @@
         <v>11</v>
       </c>
       <c r="C14" s="3" t="s">
+        <v>36</v>
+      </c>
+      <c r="D14" s="3" t="s">
         <v>37</v>
-      </c>
-      <c r="D14" s="3" t="s">
-        <v>38</v>
       </c>
       <c r="E14" s="3" t="s">
         <v>17</v>
       </c>
       <c r="F14" s="3" t="s">
-        <v>37</v>
+        <v>36</v>
       </c>
     </row>
     <row r="15" ht="16.5" customHeight="1" spans="1:6">
@@ -2093,16 +2102,16 @@
         <v>1001</v>
       </c>
       <c r="C15" s="3" t="s">
+        <v>38</v>
+      </c>
+      <c r="D15" s="3" t="s">
         <v>39</v>
       </c>
-      <c r="D15" s="3" t="s">
+      <c r="E15" s="3" t="s">
         <v>40</v>
       </c>
-      <c r="E15" s="3" t="s">
-        <v>41</v>
-      </c>
       <c r="F15" s="3" t="s">
-        <v>39</v>
+        <v>38</v>
       </c>
     </row>
     <row r="16" ht="16.5" customHeight="1" spans="1:6">
@@ -2111,16 +2120,16 @@
         <v>1002</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>41</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>42</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>43</v>
-      </c>
       <c r="E16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>41</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>42</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:6">
@@ -2129,16 +2138,16 @@
         <v>1003</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>43</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="D17" s="3" t="s">
-        <v>45</v>
-      </c>
       <c r="E17" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F17" s="3" t="s">
-        <v>44</v>
+        <v>43</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:6">
@@ -2147,16 +2156,16 @@
         <v>1004</v>
       </c>
       <c r="C18" s="3" t="s">
+        <v>45</v>
+      </c>
+      <c r="D18" s="3" t="s">
         <v>46</v>
       </c>
-      <c r="D18" s="3" t="s">
-        <v>47</v>
-      </c>
       <c r="E18" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F18" s="3" t="s">
-        <v>46</v>
+        <v>45</v>
       </c>
     </row>
     <row r="19" ht="16.5" customHeight="1" spans="1:6">
@@ -2165,16 +2174,16 @@
         <v>1005</v>
       </c>
       <c r="C19" s="3" t="s">
+        <v>47</v>
+      </c>
+      <c r="D19" s="3" t="s">
         <v>48</v>
       </c>
-      <c r="D19" s="3" t="s">
-        <v>49</v>
-      </c>
       <c r="E19" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F19" s="3" t="s">
-        <v>48</v>
+        <v>47</v>
       </c>
     </row>
     <row r="20" ht="16.5" customHeight="1" spans="1:6">
@@ -2183,16 +2192,16 @@
         <v>1006</v>
       </c>
       <c r="C20" s="3" t="s">
+        <v>49</v>
+      </c>
+      <c r="D20" s="3" t="s">
         <v>50</v>
       </c>
-      <c r="D20" s="3" t="s">
-        <v>51</v>
-      </c>
       <c r="E20" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F20" s="3" t="s">
-        <v>50</v>
+        <v>49</v>
       </c>
     </row>
     <row r="21" ht="16.5" customHeight="1" spans="1:6">
@@ -2201,16 +2210,16 @@
         <v>1007</v>
       </c>
       <c r="C21" s="3" t="s">
+        <v>51</v>
+      </c>
+      <c r="D21" s="3" t="s">
         <v>52</v>
       </c>
-      <c r="D21" s="3" t="s">
-        <v>53</v>
-      </c>
       <c r="E21" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F21" s="3" t="s">
-        <v>52</v>
+        <v>51</v>
       </c>
     </row>
     <row r="22" ht="16.5" customHeight="1" spans="1:6">
@@ -2219,16 +2228,16 @@
         <v>1008</v>
       </c>
       <c r="C22" s="3" t="s">
+        <v>53</v>
+      </c>
+      <c r="D22" s="3" t="s">
         <v>54</v>
       </c>
-      <c r="D22" s="3" t="s">
-        <v>55</v>
-      </c>
       <c r="E22" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F22" s="3" t="s">
-        <v>54</v>
+        <v>53</v>
       </c>
     </row>
     <row r="23" ht="16.5" customHeight="1" spans="1:6">
@@ -2237,16 +2246,16 @@
         <v>1051</v>
       </c>
       <c r="C23" s="3" t="s">
+        <v>55</v>
+      </c>
+      <c r="D23" s="3" t="s">
         <v>56</v>
       </c>
-      <c r="D23" s="3" t="s">
-        <v>57</v>
-      </c>
       <c r="E23" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F23" s="3" t="s">
-        <v>56</v>
+        <v>55</v>
       </c>
     </row>
     <row r="24" ht="16.5" customHeight="1" spans="1:6">
@@ -2255,16 +2264,16 @@
         <v>1201</v>
       </c>
       <c r="C24" s="3" t="s">
+        <v>57</v>
+      </c>
+      <c r="D24" s="3" t="s">
         <v>58</v>
       </c>
-      <c r="D24" s="3" t="s">
-        <v>59</v>
-      </c>
       <c r="E24" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F24" s="3" t="s">
-        <v>58</v>
+        <v>57</v>
       </c>
     </row>
     <row r="25" ht="16.5" customHeight="1" spans="1:6">
@@ -2273,16 +2282,16 @@
         <v>1801</v>
       </c>
       <c r="C25" s="3" t="s">
+        <v>59</v>
+      </c>
+      <c r="D25" s="4" t="s">
         <v>60</v>
       </c>
-      <c r="D25" s="4" t="s">
-        <v>61</v>
-      </c>
       <c r="E25" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F25" s="3" t="s">
-        <v>60</v>
+        <v>59</v>
       </c>
     </row>
     <row r="26" ht="16.5" customHeight="1" spans="1:6">
@@ -2291,16 +2300,16 @@
         <v>1802</v>
       </c>
       <c r="C26" s="3" t="s">
-        <v>62</v>
+        <v>61</v>
       </c>
       <c r="D26" s="4" t="s">
+        <v>60</v>
+      </c>
+      <c r="E26" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="F26" s="3" t="s">
         <v>61</v>
-      </c>
-      <c r="E26" s="3" t="s">
-        <v>41</v>
-      </c>
-      <c r="F26" s="3" t="s">
-        <v>62</v>
       </c>
     </row>
     <row r="27" ht="16.5" customHeight="1" spans="1:6">
@@ -2309,16 +2318,16 @@
         <v>1803</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>63</v>
+        <v>62</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:6">
@@ -2327,16 +2336,16 @@
         <v>1804</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>64</v>
+        <v>63</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:6">
@@ -2345,16 +2354,16 @@
         <v>1805</v>
       </c>
       <c r="C29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
       <c r="D29" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E29" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>65</v>
+        <v>64</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:6">
@@ -2363,16 +2372,16 @@
         <v>1806</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>66</v>
+        <v>65</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:6">
@@ -2381,34 +2390,34 @@
         <v>1807</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>67</v>
+        <v>66</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>61</v>
+        <v>60</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>41</v>
+        <v>40</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>67</v>
-      </c>
-    </row>
-    <row r="32" ht="16.5" customHeight="1" spans="1:6">
+        <v>66</v>
+      </c>
+    </row>
+    <row r="32" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
         <v>2001</v>
       </c>
       <c r="C32" s="3" t="s">
+        <v>67</v>
+      </c>
+      <c r="D32" s="3" t="s">
         <v>68</v>
       </c>
-      <c r="D32" s="3" t="s">
+      <c r="E32" s="3" t="s">
         <v>69</v>
       </c>
-      <c r="E32" s="3" t="s">
-        <v>70</v>
-      </c>
       <c r="F32" s="3" t="s">
-        <v>68</v>
+        <v>67</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:6">
@@ -2417,16 +2426,16 @@
         <v>2002</v>
       </c>
       <c r="C33" s="3" t="s">
+        <v>70</v>
+      </c>
+      <c r="D33" s="3" t="s">
         <v>71</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>72</v>
-      </c>
       <c r="E33" s="3" t="s">
+        <v>69</v>
+      </c>
+      <c r="F33" s="3" t="s">
         <v>70</v>
-      </c>
-      <c r="F33" s="3" t="s">
-        <v>71</v>
       </c>
     </row>
     <row r="34" ht="16.5" customHeight="1" spans="1:6">
@@ -2435,16 +2444,16 @@
         <v>2003</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>72</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="D34" s="3" t="s">
-        <v>74</v>
-      </c>
       <c r="E34" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F34" s="3" t="s">
-        <v>73</v>
+        <v>72</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:6">
@@ -2453,16 +2462,16 @@
         <v>2004</v>
       </c>
       <c r="C35" s="3" t="s">
+        <v>74</v>
+      </c>
+      <c r="D35" s="3" t="s">
         <v>75</v>
       </c>
-      <c r="D35" s="3" t="s">
-        <v>76</v>
-      </c>
       <c r="E35" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F35" s="3" t="s">
-        <v>75</v>
+        <v>74</v>
       </c>
     </row>
     <row r="36" ht="16.5" customHeight="1" spans="1:6">
@@ -2471,16 +2480,16 @@
         <v>2005</v>
       </c>
       <c r="C36" s="3" t="s">
+        <v>76</v>
+      </c>
+      <c r="D36" s="3" t="s">
         <v>77</v>
       </c>
-      <c r="D36" s="3" t="s">
-        <v>78</v>
-      </c>
       <c r="E36" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F36" s="3" t="s">
-        <v>77</v>
+        <v>76</v>
       </c>
     </row>
     <row r="37" ht="16.5" customHeight="1" spans="1:6">
@@ -2489,16 +2498,16 @@
         <v>2006</v>
       </c>
       <c r="C37" s="3" t="s">
+        <v>78</v>
+      </c>
+      <c r="D37" s="3" t="s">
         <v>79</v>
       </c>
-      <c r="D37" s="3" t="s">
-        <v>80</v>
-      </c>
       <c r="E37" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F37" s="3" t="s">
-        <v>79</v>
+        <v>78</v>
       </c>
     </row>
     <row r="38" ht="16.5" customHeight="1" spans="1:6">
@@ -2507,16 +2516,16 @@
         <v>2007</v>
       </c>
       <c r="C38" s="3" t="s">
+        <v>80</v>
+      </c>
+      <c r="D38" s="3" t="s">
         <v>81</v>
       </c>
-      <c r="D38" s="3" t="s">
-        <v>82</v>
-      </c>
       <c r="E38" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F38" s="3" t="s">
-        <v>81</v>
+        <v>80</v>
       </c>
     </row>
     <row r="39" ht="16.5" customHeight="1" spans="1:6">
@@ -2525,16 +2534,16 @@
         <v>2008</v>
       </c>
       <c r="C39" s="3" t="s">
+        <v>82</v>
+      </c>
+      <c r="D39" s="3" t="s">
         <v>83</v>
       </c>
-      <c r="D39" s="3" t="s">
-        <v>84</v>
-      </c>
       <c r="E39" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F39" s="3" t="s">
-        <v>83</v>
+        <v>82</v>
       </c>
     </row>
     <row r="40" ht="16.5" customHeight="1" spans="1:6">
@@ -2543,16 +2552,16 @@
         <v>2009</v>
       </c>
       <c r="C40" s="3" t="s">
+        <v>84</v>
+      </c>
+      <c r="D40" s="3" t="s">
         <v>85</v>
       </c>
-      <c r="D40" s="3" t="s">
-        <v>86</v>
-      </c>
       <c r="E40" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F40" s="3" t="s">
-        <v>85</v>
+        <v>84</v>
       </c>
     </row>
     <row r="41" ht="16.5" customHeight="1" spans="1:6">
@@ -2561,16 +2570,16 @@
         <v>2010</v>
       </c>
       <c r="C41" s="3" t="s">
+        <v>86</v>
+      </c>
+      <c r="D41" s="3" t="s">
         <v>87</v>
       </c>
-      <c r="D41" s="3" t="s">
-        <v>88</v>
-      </c>
       <c r="E41" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F41" s="3" t="s">
-        <v>87</v>
+        <v>86</v>
       </c>
     </row>
     <row r="42" ht="16.5" customHeight="1" spans="1:6">
@@ -2579,16 +2588,16 @@
         <v>2011</v>
       </c>
       <c r="C42" s="3" t="s">
+        <v>88</v>
+      </c>
+      <c r="D42" s="3" t="s">
         <v>89</v>
       </c>
-      <c r="D42" s="3" t="s">
-        <v>90</v>
-      </c>
       <c r="E42" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F42" s="3" t="s">
-        <v>89</v>
+        <v>88</v>
       </c>
     </row>
     <row r="43" ht="16.5" customHeight="1" spans="1:6">
@@ -2597,589 +2606,591 @@
         <v>2012</v>
       </c>
       <c r="C43" s="3" t="s">
+        <v>90</v>
+      </c>
+      <c r="D43" s="3" t="s">
         <v>91</v>
       </c>
-      <c r="D43" s="3" t="s">
-        <v>92</v>
-      </c>
       <c r="E43" s="3" t="s">
-        <v>70</v>
+        <v>69</v>
       </c>
       <c r="F43" s="3" t="s">
-        <v>91</v>
+        <v>90</v>
       </c>
     </row>
     <row r="44" ht="16.5" customHeight="1" spans="1:6">
       <c r="A44" s="3"/>
       <c r="B44" s="3">
-        <v>5001</v>
+        <v>2013</v>
       </c>
       <c r="C44" s="3" t="s">
+        <v>92</v>
+      </c>
+      <c r="D44" s="3" t="s">
         <v>93</v>
       </c>
-      <c r="D44" s="3" t="s">
-        <v>94</v>
-      </c>
       <c r="E44" s="3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F44" s="3" t="s">
-        <v>93</v>
+        <v>92</v>
       </c>
     </row>
     <row r="45" ht="16.5" customHeight="1" spans="1:6">
       <c r="A45" s="3"/>
       <c r="B45" s="3">
-        <v>5002</v>
+        <v>2014</v>
       </c>
       <c r="C45" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
       <c r="D45" s="3" t="s">
-        <v>97</v>
+        <v>95</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>95</v>
+        <v>69</v>
       </c>
       <c r="F45" s="3" t="s">
-        <v>96</v>
+        <v>94</v>
       </c>
     </row>
     <row r="46" ht="16.5" customHeight="1" spans="1:6">
       <c r="A46" s="3"/>
       <c r="B46" s="3">
-        <v>5003</v>
+        <v>5001</v>
       </c>
       <c r="C46" s="3" t="s">
+        <v>96</v>
+      </c>
+      <c r="D46" s="3" t="s">
+        <v>97</v>
+      </c>
+      <c r="E46" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="D46" s="3" t="s">
-        <v>99</v>
-      </c>
-      <c r="E46" s="3" t="s">
-        <v>95</v>
-      </c>
       <c r="F46" s="3" t="s">
-        <v>98</v>
+        <v>96</v>
       </c>
     </row>
     <row r="47" ht="16.5" customHeight="1" spans="1:6">
       <c r="A47" s="3"/>
       <c r="B47" s="3">
-        <v>5101</v>
+        <v>5002</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>99</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>100</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>101</v>
-      </c>
       <c r="E47" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F47" s="3" t="s">
-        <v>100</v>
+        <v>99</v>
       </c>
     </row>
     <row r="48" ht="16.5" customHeight="1" spans="1:6">
       <c r="A48" s="3"/>
       <c r="B48" s="3">
-        <v>5102</v>
+        <v>5003</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>101</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>102</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>103</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>102</v>
+        <v>101</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:6">
       <c r="A49" s="3"/>
       <c r="B49" s="3">
-        <v>5103</v>
+        <v>5101</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>103</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="D49" s="3" t="s">
-        <v>105</v>
-      </c>
       <c r="E49" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F49" s="3" t="s">
-        <v>104</v>
+        <v>103</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:6">
       <c r="A50" s="3"/>
       <c r="B50" s="3">
-        <v>5104</v>
+        <v>5102</v>
       </c>
       <c r="C50" s="3" t="s">
+        <v>105</v>
+      </c>
+      <c r="D50" s="3" t="s">
         <v>106</v>
       </c>
-      <c r="D50" s="3" t="s">
-        <v>107</v>
-      </c>
       <c r="E50" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F50" s="3" t="s">
-        <v>106</v>
+        <v>105</v>
       </c>
     </row>
     <row r="51" ht="16.5" customHeight="1" spans="1:6">
       <c r="A51" s="3"/>
       <c r="B51" s="3">
-        <v>5105</v>
+        <v>5103</v>
       </c>
       <c r="C51" s="3" t="s">
+        <v>107</v>
+      </c>
+      <c r="D51" s="3" t="s">
         <v>108</v>
       </c>
-      <c r="D51" s="3" t="s">
-        <v>109</v>
-      </c>
       <c r="E51" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F51" s="3" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
     </row>
     <row r="52" ht="16.5" customHeight="1" spans="1:6">
       <c r="A52" s="3"/>
       <c r="B52" s="3">
-        <v>5106</v>
+        <v>5104</v>
       </c>
       <c r="C52" s="3" t="s">
+        <v>109</v>
+      </c>
+      <c r="D52" s="3" t="s">
         <v>110</v>
       </c>
-      <c r="D52" s="3" t="s">
-        <v>111</v>
-      </c>
       <c r="E52" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F52" s="3" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
     </row>
     <row r="53" ht="16.5" customHeight="1" spans="1:6">
       <c r="A53" s="3"/>
       <c r="B53" s="3">
-        <v>5107</v>
+        <v>5105</v>
       </c>
       <c r="C53" s="3" t="s">
+        <v>111</v>
+      </c>
+      <c r="D53" s="3" t="s">
         <v>112</v>
       </c>
-      <c r="D53" s="3" t="s">
-        <v>113</v>
-      </c>
       <c r="E53" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F53" s="3" t="s">
-        <v>112</v>
+        <v>111</v>
       </c>
     </row>
     <row r="54" ht="16.5" customHeight="1" spans="1:6">
       <c r="A54" s="3"/>
       <c r="B54" s="3">
-        <v>5201</v>
+        <v>5106</v>
       </c>
       <c r="C54" s="3" t="s">
+        <v>113</v>
+      </c>
+      <c r="D54" s="3" t="s">
         <v>114</v>
       </c>
-      <c r="D54" s="3" t="s">
-        <v>115</v>
-      </c>
       <c r="E54" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F54" s="3" t="s">
-        <v>114</v>
+        <v>113</v>
       </c>
     </row>
     <row r="55" ht="16.5" customHeight="1" spans="1:6">
       <c r="A55" s="3"/>
       <c r="B55" s="3">
-        <v>5202</v>
+        <v>5107</v>
       </c>
       <c r="C55" s="3" t="s">
+        <v>115</v>
+      </c>
+      <c r="D55" s="3" t="s">
         <v>116</v>
       </c>
-      <c r="D55" s="3" t="s">
-        <v>117</v>
-      </c>
       <c r="E55" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F55" s="3" t="s">
-        <v>116</v>
+        <v>115</v>
       </c>
     </row>
     <row r="56" ht="16.5" customHeight="1" spans="1:6">
       <c r="A56" s="3"/>
       <c r="B56" s="3">
-        <v>5301</v>
+        <v>5201</v>
       </c>
       <c r="C56" s="3" t="s">
+        <v>117</v>
+      </c>
+      <c r="D56" s="3" t="s">
         <v>118</v>
       </c>
-      <c r="D56" s="3" t="s">
-        <v>119</v>
-      </c>
       <c r="E56" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F56" s="3" t="s">
-        <v>118</v>
+        <v>117</v>
       </c>
     </row>
     <row r="57" ht="16.5" customHeight="1" spans="1:6">
       <c r="A57" s="3"/>
       <c r="B57" s="3">
-        <v>5302</v>
+        <v>5202</v>
       </c>
       <c r="C57" s="3" t="s">
+        <v>119</v>
+      </c>
+      <c r="D57" s="3" t="s">
         <v>120</v>
       </c>
-      <c r="D57" s="3" t="s">
-        <v>121</v>
-      </c>
       <c r="E57" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F57" s="3" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
     </row>
     <row r="58" ht="16.5" customHeight="1" spans="1:6">
       <c r="A58" s="3"/>
       <c r="B58" s="3">
-        <v>5501</v>
+        <v>5301</v>
       </c>
       <c r="C58" s="3" t="s">
+        <v>121</v>
+      </c>
+      <c r="D58" s="3" t="s">
         <v>122</v>
       </c>
-      <c r="D58" s="3" t="s">
-        <v>123</v>
-      </c>
       <c r="E58" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F58" s="3" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
     </row>
     <row r="59" ht="16.5" customHeight="1" spans="1:6">
       <c r="A59" s="3"/>
       <c r="B59" s="3">
-        <v>5502</v>
+        <v>5302</v>
       </c>
       <c r="C59" s="3" t="s">
+        <v>123</v>
+      </c>
+      <c r="D59" s="3" t="s">
         <v>124</v>
       </c>
-      <c r="D59" s="3" t="s">
-        <v>125</v>
-      </c>
       <c r="E59" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F59" s="3" t="s">
-        <v>124</v>
+        <v>123</v>
       </c>
     </row>
     <row r="60" ht="16.5" customHeight="1" spans="1:6">
       <c r="A60" s="3"/>
       <c r="B60" s="3">
-        <v>5503</v>
+        <v>5528</v>
       </c>
       <c r="C60" s="3" t="s">
+        <v>125</v>
+      </c>
+      <c r="D60" s="3" t="s">
         <v>126</v>
       </c>
-      <c r="D60" s="3" t="s">
-        <v>127</v>
-      </c>
       <c r="E60" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F60" s="3" t="s">
-        <v>126</v>
+        <v>125</v>
       </c>
     </row>
     <row r="61" ht="16.5" customHeight="1" spans="1:6">
       <c r="A61" s="3"/>
       <c r="B61" s="3">
-        <v>5504</v>
+        <v>5529</v>
       </c>
       <c r="C61" s="3" t="s">
+        <v>127</v>
+      </c>
+      <c r="D61" s="3" t="s">
         <v>128</v>
       </c>
-      <c r="D61" s="3" t="s">
-        <v>129</v>
-      </c>
       <c r="E61" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F61" s="3" t="s">
-        <v>128</v>
+        <v>127</v>
       </c>
     </row>
     <row r="62" ht="16.5" customHeight="1" spans="1:6">
       <c r="A62" s="3"/>
       <c r="B62" s="3">
-        <v>5505</v>
+        <v>5530</v>
       </c>
       <c r="C62" s="3" t="s">
+        <v>129</v>
+      </c>
+      <c r="D62" s="3" t="s">
         <v>130</v>
       </c>
-      <c r="D62" s="3" t="s">
-        <v>131</v>
-      </c>
       <c r="E62" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F62" s="3" t="s">
-        <v>130</v>
+        <v>129</v>
       </c>
     </row>
     <row r="63" ht="16.5" customHeight="1" spans="1:6">
       <c r="A63" s="3"/>
       <c r="B63" s="3">
-        <v>5506</v>
+        <v>5531</v>
       </c>
       <c r="C63" s="3" t="s">
+        <v>131</v>
+      </c>
+      <c r="D63" s="3" t="s">
         <v>132</v>
       </c>
-      <c r="D63" s="3" t="s">
-        <v>133</v>
-      </c>
       <c r="E63" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F63" s="3" t="s">
-        <v>132</v>
+        <v>131</v>
       </c>
     </row>
     <row r="64" ht="16.5" customHeight="1" spans="1:6">
       <c r="A64" s="3"/>
       <c r="B64" s="3">
-        <v>5507</v>
+        <v>5532</v>
       </c>
       <c r="C64" s="3" t="s">
+        <v>133</v>
+      </c>
+      <c r="D64" s="3" t="s">
         <v>134</v>
       </c>
-      <c r="D64" s="3" t="s">
-        <v>135</v>
-      </c>
       <c r="E64" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F64" s="3" t="s">
-        <v>134</v>
+        <v>133</v>
       </c>
     </row>
     <row r="65" ht="16.5" customHeight="1" spans="1:6">
       <c r="A65" s="3"/>
       <c r="B65" s="3">
-        <v>5508</v>
+        <v>5533</v>
       </c>
       <c r="C65" s="3" t="s">
+        <v>135</v>
+      </c>
+      <c r="D65" s="3" t="s">
         <v>136</v>
       </c>
-      <c r="D65" s="3" t="s">
-        <v>137</v>
-      </c>
       <c r="E65" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F65" s="3" t="s">
-        <v>136</v>
+        <v>135</v>
       </c>
     </row>
     <row r="66" ht="16.5" customHeight="1" spans="1:6">
       <c r="A66" s="3"/>
       <c r="B66" s="3">
-        <v>5509</v>
+        <v>5534</v>
       </c>
       <c r="C66" s="3" t="s">
+        <v>137</v>
+      </c>
+      <c r="D66" s="3" t="s">
         <v>138</v>
       </c>
-      <c r="D66" s="3" t="s">
-        <v>139</v>
-      </c>
       <c r="E66" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F66" s="3" t="s">
-        <v>138</v>
+        <v>137</v>
       </c>
     </row>
     <row r="67" ht="16.5" customHeight="1" spans="1:6">
       <c r="A67" s="3"/>
       <c r="B67" s="3">
-        <v>5510</v>
+        <v>5535</v>
       </c>
       <c r="C67" s="3" t="s">
+        <v>139</v>
+      </c>
+      <c r="D67" s="3" t="s">
         <v>140</v>
       </c>
-      <c r="D67" s="3" t="s">
-        <v>141</v>
-      </c>
       <c r="E67" s="3" t="s">
-        <v>95</v>
+        <v>98</v>
       </c>
       <c r="F67" s="3" t="s">
-        <v>140</v>
+        <v>139</v>
       </c>
     </row>
     <row r="68" ht="16.5" customHeight="1" spans="1:6">
       <c r="A68" s="3"/>
       <c r="B68" s="3">
-        <v>10001</v>
+        <v>5536</v>
       </c>
       <c r="C68" s="3" t="s">
+        <v>141</v>
+      </c>
+      <c r="D68" s="3" t="s">
         <v>142</v>
       </c>
-      <c r="D68" s="3" t="s">
-        <v>143</v>
-      </c>
       <c r="E68" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F68" s="3" t="s">
-        <v>145</v>
+        <v>141</v>
       </c>
     </row>
     <row r="69" ht="16.5" customHeight="1" spans="1:6">
       <c r="A69" s="3"/>
       <c r="B69" s="3">
-        <v>10002</v>
+        <v>5537</v>
       </c>
       <c r="C69" s="3" t="s">
-        <v>146</v>
+        <v>143</v>
       </c>
       <c r="D69" s="3" t="s">
-        <v>147</v>
+        <v>144</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>144</v>
+        <v>98</v>
       </c>
       <c r="F69" s="3" t="s">
-        <v>148</v>
+        <v>143</v>
       </c>
     </row>
     <row r="70" ht="16.5" customHeight="1" spans="1:6">
       <c r="A70" s="3"/>
       <c r="B70" s="3">
-        <v>10003</v>
+        <v>10001</v>
       </c>
       <c r="C70" s="3" t="s">
-        <v>149</v>
+        <v>145</v>
       </c>
       <c r="D70" s="3" t="s">
-        <v>150</v>
+        <v>146</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>151</v>
+        <v>148</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:6">
       <c r="A71" s="3"/>
       <c r="B71" s="3">
-        <v>10004</v>
+        <v>10002</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E71" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F71" s="3" t="s">
-        <v>154</v>
+        <v>151</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="1:6">
       <c r="A72" s="3"/>
       <c r="B72" s="3">
-        <v>11001</v>
+        <v>10003</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>155</v>
+        <v>152</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>156</v>
+        <v>153</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="1:6">
       <c r="A73" s="3"/>
       <c r="B73" s="3">
-        <v>12001</v>
+        <v>10004</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>158</v>
+        <v>155</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>159</v>
+        <v>156</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>160</v>
-      </c>
-    </row>
-    <row r="74" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="74" ht="16.5" customHeight="1" spans="1:6">
       <c r="A74" s="3"/>
       <c r="B74" s="3">
-        <v>20001</v>
+        <v>10005</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>158</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>159</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>160</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" spans="1:6">
+      <c r="A75" s="3" t="s">
+        <v>3</v>
+      </c>
+      <c r="B75" s="3">
+        <v>12001</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>161</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>162</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F74" s="3" t="s">
-        <v>161</v>
-      </c>
-    </row>
-    <row r="75" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A75" s="3"/>
-      <c r="B75" s="3">
-        <v>20002</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>163</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>164</v>
-      </c>
       <c r="E75" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F75" s="3" t="s">
         <v>163</v>
@@ -3188,149 +3199,219 @@
     <row r="76" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A76" s="3"/>
       <c r="B76" s="3">
-        <v>20003</v>
+        <v>12001</v>
       </c>
       <c r="C76" s="3" t="s">
+        <v>164</v>
+      </c>
+      <c r="D76" s="3" t="s">
         <v>165</v>
       </c>
-      <c r="D76" s="3" t="s">
-        <v>166</v>
-      </c>
       <c r="E76" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
     </row>
     <row r="77" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A77" s="3"/>
       <c r="B77" s="3">
-        <v>20004</v>
+        <v>12002</v>
       </c>
       <c r="C77" s="3" t="s">
+        <v>166</v>
+      </c>
+      <c r="D77" s="3" t="s">
         <v>167</v>
       </c>
-      <c r="D77" s="3" t="s">
-        <v>168</v>
-      </c>
       <c r="E77" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F77" s="3" t="s">
-        <v>167</v>
+        <v>166</v>
       </c>
     </row>
     <row r="78" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A78" s="3"/>
       <c r="B78" s="3">
-        <v>20005</v>
+        <v>12003</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>168</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>169</v>
       </c>
-      <c r="D78" s="3" t="s">
-        <v>170</v>
-      </c>
       <c r="E78" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F78" s="3" t="s">
-        <v>169</v>
+        <v>168</v>
       </c>
     </row>
     <row r="79" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A79" s="3"/>
       <c r="B79" s="3">
-        <v>20006</v>
+        <v>12004</v>
       </c>
       <c r="C79" s="3" t="s">
+        <v>170</v>
+      </c>
+      <c r="D79" s="3" t="s">
         <v>171</v>
       </c>
-      <c r="D79" s="3" t="s">
-        <v>172</v>
-      </c>
       <c r="E79" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F79" s="3" t="s">
-        <v>171</v>
+        <v>170</v>
       </c>
     </row>
     <row r="80" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A80" s="3"/>
       <c r="B80" s="3">
-        <v>20007</v>
+        <v>12005</v>
       </c>
       <c r="C80" s="3" t="s">
+        <v>172</v>
+      </c>
+      <c r="D80" s="3" t="s">
         <v>173</v>
       </c>
-      <c r="D80" s="3" t="s">
-        <v>174</v>
-      </c>
       <c r="E80" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F80" s="3" t="s">
-        <v>173</v>
+        <v>172</v>
       </c>
     </row>
     <row r="81" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A81" s="3"/>
       <c r="B81" s="3">
-        <v>20008</v>
+        <v>12006</v>
       </c>
       <c r="C81" s="3" t="s">
+        <v>174</v>
+      </c>
+      <c r="D81" s="3" t="s">
         <v>175</v>
       </c>
-      <c r="D81" s="3" t="s">
-        <v>176</v>
-      </c>
       <c r="E81" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F81" s="3" t="s">
-        <v>175</v>
-      </c>
-    </row>
-    <row r="82" customFormat="1" ht="16.5" spans="1:6">
+        <v>174</v>
+      </c>
+    </row>
+    <row r="82" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A82" s="3"/>
       <c r="B82" s="3">
-        <v>30001</v>
+        <v>12007</v>
       </c>
       <c r="C82" s="3" t="s">
+        <v>176</v>
+      </c>
+      <c r="D82" s="3" t="s">
         <v>177</v>
       </c>
-      <c r="D82" s="3" t="s">
-        <v>178</v>
-      </c>
       <c r="E82" s="3" t="s">
-        <v>144</v>
+        <v>147</v>
       </c>
       <c r="F82" s="3" t="s">
-        <v>177</v>
-      </c>
-    </row>
-    <row r="83" customFormat="1" ht="16.5" spans="1:6">
+        <v>176</v>
+      </c>
+    </row>
+    <row r="83" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A83" s="3"/>
       <c r="B83" s="3">
-        <v>30005</v>
+        <v>12008</v>
       </c>
       <c r="C83" s="3" t="s">
+        <v>178</v>
+      </c>
+      <c r="D83" s="3" t="s">
         <v>179</v>
       </c>
-      <c r="D83" s="3" t="s">
+      <c r="E83" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F83" s="3" t="s">
+        <v>178</v>
+      </c>
+    </row>
+    <row r="84" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A84" s="3"/>
+      <c r="B84" s="3">
+        <v>13001</v>
+      </c>
+      <c r="C84" s="3" t="s">
         <v>180</v>
       </c>
-      <c r="E83" s="3" t="s">
-        <v>144</v>
-      </c>
-      <c r="F83" s="3" t="s">
-        <v>179</v>
+      <c r="D84" s="3" t="s">
+        <v>181</v>
+      </c>
+      <c r="E84" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F84" s="3" t="s">
+        <v>180</v>
+      </c>
+    </row>
+    <row r="85" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A85" s="3"/>
+      <c r="B85" s="3">
+        <v>13002</v>
+      </c>
+      <c r="C85" s="3" t="s">
+        <v>182</v>
+      </c>
+      <c r="D85" s="3" t="s">
+        <v>183</v>
+      </c>
+      <c r="E85" s="3" t="s">
+        <v>147</v>
+      </c>
+      <c r="F85" s="3" t="s">
+        <v>182</v>
       </c>
     </row>
   </sheetData>
   <conditionalFormatting sqref="E4">
+    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10">
+    <cfRule type="cellIs" dxfId="0" priority="45" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="40" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="35" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="30" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="4" priority="25" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
@@ -3347,105 +3428,88 @@
       <formula>"其他"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" dxfId="0" priority="35" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="30" operator="equal">
+  <conditionalFormatting sqref="E76">
+    <cfRule type="cellIs" dxfId="4" priority="126" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="127" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="128" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="129" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="25" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="20" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="15" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E74">
-    <cfRule type="cellIs" dxfId="4" priority="116" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="117" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="118" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="119" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="120" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="130" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E9">
-    <cfRule type="cellIs" dxfId="4" priority="36" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="46" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="37" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="47" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="38" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="48" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="39" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="49" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="40" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="50" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E11:E14">
-    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E75:E83">
-    <cfRule type="cellIs" dxfId="4" priority="76" operator="equal">
+  <conditionalFormatting sqref="E77:E85">
+    <cfRule type="cellIs" dxfId="4" priority="86" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="77" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="87" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="78" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="88" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="79" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="89" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="80" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="90" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E73 E84:E1048576">
-    <cfRule type="cellIs" dxfId="4" priority="121" operator="equal">
+  <conditionalFormatting sqref="E15:E31 E33:E75 E86:E1048576">
+    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="122" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="123" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="124" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="134" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="125" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="135" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>

--- a/RaidenDemo/文档/配置表/EffectResource.xlsx
+++ b/RaidenDemo/文档/配置表/EffectResource.xlsx
@@ -79,7 +79,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="346" uniqueCount="184">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="358" uniqueCount="190">
   <si>
     <t>##var</t>
   </si>
@@ -174,7 +174,19 @@
     <t>shootFire_1007</t>
   </si>
   <si>
-    <t>横向发光-蓝色</t>
+    <t>闪光-蓝色</t>
+  </si>
+  <si>
+    <t>shootFire_1008</t>
+  </si>
+  <si>
+    <t>小型散光-青色</t>
+  </si>
+  <si>
+    <t>shootFire_1009</t>
+  </si>
+  <si>
+    <t>小型散光-绿色</t>
   </si>
   <si>
     <t>shootFire_2001</t>
@@ -366,7 +378,13 @@
     <t>hit_13</t>
   </si>
   <si>
-    <t>刺闪-红色2</t>
+    <t>敌方子弹的通用命中特效：刺闪-红色2</t>
+  </si>
+  <si>
+    <t>hit_14</t>
+  </si>
+  <si>
+    <t>刺闪-黄黑</t>
   </si>
   <si>
     <t>explosion_small_1</t>
@@ -1828,13 +1846,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:etc="http://www.wps.cn/officeDocument/2017/etCustomData">
   <sheetPr/>
-  <dimension ref="A1:F85"/>
+  <dimension ref="A1:F88"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25" outlineLevelCol="5"/>
   <cols>
     <col min="1" max="1" width="8" customWidth="1"/>
     <col min="2" max="2" width="12" customWidth="1"/>
     <col min="3" max="3" width="26.375" customWidth="1"/>
-    <col min="4" max="4" width="30.125" customWidth="1"/>
+    <col min="4" max="4" width="35.875" customWidth="1"/>
     <col min="5" max="5" width="11.125" customWidth="1"/>
     <col min="6" max="6" width="24" customWidth="1"/>
     <col min="7" max="7" width="15" customWidth="1"/>
@@ -2081,7 +2099,7 @@
     <row r="14" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A14" s="3"/>
       <c r="B14" s="3">
-        <v>11</v>
+        <v>201</v>
       </c>
       <c r="C14" s="3" t="s">
         <v>36</v>
@@ -2096,10 +2114,10 @@
         <v>36</v>
       </c>
     </row>
-    <row r="15" ht="16.5" customHeight="1" spans="1:6">
+    <row r="15" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A15" s="3"/>
       <c r="B15" s="3">
-        <v>1001</v>
+        <v>202</v>
       </c>
       <c r="C15" s="3" t="s">
         <v>38</v>
@@ -2108,52 +2126,52 @@
         <v>39</v>
       </c>
       <c r="E15" s="3" t="s">
-        <v>40</v>
+        <v>17</v>
       </c>
       <c r="F15" s="3" t="s">
         <v>38</v>
       </c>
     </row>
-    <row r="16" ht="16.5" customHeight="1" spans="1:6">
+    <row r="16" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A16" s="3"/>
       <c r="B16" s="3">
-        <v>1002</v>
+        <v>203</v>
       </c>
       <c r="C16" s="3" t="s">
+        <v>40</v>
+      </c>
+      <c r="D16" s="3" t="s">
         <v>41</v>
       </c>
-      <c r="D16" s="3" t="s">
-        <v>42</v>
-      </c>
       <c r="E16" s="3" t="s">
+        <v>17</v>
+      </c>
+      <c r="F16" s="3" t="s">
         <v>40</v>
-      </c>
-      <c r="F16" s="3" t="s">
-        <v>41</v>
       </c>
     </row>
     <row r="17" ht="16.5" customHeight="1" spans="1:6">
       <c r="A17" s="3"/>
       <c r="B17" s="3">
-        <v>1003</v>
+        <v>1001</v>
       </c>
       <c r="C17" s="3" t="s">
+        <v>42</v>
+      </c>
+      <c r="D17" s="3" t="s">
         <v>43</v>
       </c>
-      <c r="D17" s="3" t="s">
+      <c r="E17" s="3" t="s">
         <v>44</v>
       </c>
-      <c r="E17" s="3" t="s">
-        <v>40</v>
-      </c>
       <c r="F17" s="3" t="s">
-        <v>43</v>
+        <v>42</v>
       </c>
     </row>
     <row r="18" ht="16.5" customHeight="1" spans="1:6">
       <c r="A18" s="3"/>
       <c r="B18" s="3">
-        <v>1004</v>
+        <v>1002</v>
       </c>
       <c r="C18" s="3" t="s">
         <v>45</v>
@@ -2162,7 +2180,7 @@
         <v>46</v>
       </c>
       <c r="E18" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F18" s="3" t="s">
         <v>45</v>
@@ -2171,7 +2189,7 @@
     <row r="19" ht="16.5" customHeight="1" spans="1:6">
       <c r="A19" s="3"/>
       <c r="B19" s="3">
-        <v>1005</v>
+        <v>1003</v>
       </c>
       <c r="C19" s="3" t="s">
         <v>47</v>
@@ -2180,7 +2198,7 @@
         <v>48</v>
       </c>
       <c r="E19" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F19" s="3" t="s">
         <v>47</v>
@@ -2189,7 +2207,7 @@
     <row r="20" ht="16.5" customHeight="1" spans="1:6">
       <c r="A20" s="3"/>
       <c r="B20" s="3">
-        <v>1006</v>
+        <v>1004</v>
       </c>
       <c r="C20" s="3" t="s">
         <v>49</v>
@@ -2198,7 +2216,7 @@
         <v>50</v>
       </c>
       <c r="E20" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F20" s="3" t="s">
         <v>49</v>
@@ -2207,7 +2225,7 @@
     <row r="21" ht="16.5" customHeight="1" spans="1:6">
       <c r="A21" s="3"/>
       <c r="B21" s="3">
-        <v>1007</v>
+        <v>1005</v>
       </c>
       <c r="C21" s="3" t="s">
         <v>51</v>
@@ -2216,7 +2234,7 @@
         <v>52</v>
       </c>
       <c r="E21" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F21" s="3" t="s">
         <v>51</v>
@@ -2225,7 +2243,7 @@
     <row r="22" ht="16.5" customHeight="1" spans="1:6">
       <c r="A22" s="3"/>
       <c r="B22" s="3">
-        <v>1008</v>
+        <v>1006</v>
       </c>
       <c r="C22" s="3" t="s">
         <v>53</v>
@@ -2234,7 +2252,7 @@
         <v>54</v>
       </c>
       <c r="E22" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F22" s="3" t="s">
         <v>53</v>
@@ -2243,7 +2261,7 @@
     <row r="23" ht="16.5" customHeight="1" spans="1:6">
       <c r="A23" s="3"/>
       <c r="B23" s="3">
-        <v>1051</v>
+        <v>1007</v>
       </c>
       <c r="C23" s="3" t="s">
         <v>55</v>
@@ -2252,7 +2270,7 @@
         <v>56</v>
       </c>
       <c r="E23" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F23" s="3" t="s">
         <v>55</v>
@@ -2261,7 +2279,7 @@
     <row r="24" ht="16.5" customHeight="1" spans="1:6">
       <c r="A24" s="3"/>
       <c r="B24" s="3">
-        <v>1201</v>
+        <v>1008</v>
       </c>
       <c r="C24" s="3" t="s">
         <v>57</v>
@@ -2270,7 +2288,7 @@
         <v>58</v>
       </c>
       <c r="E24" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F24" s="3" t="s">
         <v>57</v>
@@ -2279,16 +2297,16 @@
     <row r="25" ht="16.5" customHeight="1" spans="1:6">
       <c r="A25" s="3"/>
       <c r="B25" s="3">
-        <v>1801</v>
+        <v>1051</v>
       </c>
       <c r="C25" s="3" t="s">
         <v>59</v>
       </c>
-      <c r="D25" s="4" t="s">
+      <c r="D25" s="3" t="s">
         <v>60</v>
       </c>
       <c r="E25" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F25" s="3" t="s">
         <v>59</v>
@@ -2297,16 +2315,16 @@
     <row r="26" ht="16.5" customHeight="1" spans="1:6">
       <c r="A26" s="3"/>
       <c r="B26" s="3">
-        <v>1802</v>
+        <v>1201</v>
       </c>
       <c r="C26" s="3" t="s">
         <v>61</v>
       </c>
-      <c r="D26" s="4" t="s">
-        <v>60</v>
+      <c r="D26" s="3" t="s">
+        <v>62</v>
       </c>
       <c r="E26" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F26" s="3" t="s">
         <v>61</v>
@@ -2315,151 +2333,151 @@
     <row r="27" ht="16.5" customHeight="1" spans="1:6">
       <c r="A27" s="3"/>
       <c r="B27" s="3">
-        <v>1803</v>
+        <v>1801</v>
       </c>
       <c r="C27" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
       <c r="D27" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E27" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F27" s="3" t="s">
-        <v>62</v>
+        <v>63</v>
       </c>
     </row>
     <row r="28" ht="16.5" customHeight="1" spans="1:6">
       <c r="A28" s="3"/>
       <c r="B28" s="3">
-        <v>1804</v>
+        <v>1802</v>
       </c>
       <c r="C28" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="D28" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E28" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F28" s="3" t="s">
-        <v>63</v>
+        <v>65</v>
       </c>
     </row>
     <row r="29" ht="16.5" customHeight="1" spans="1:6">
       <c r="A29" s="3"/>
       <c r="B29" s="3">
-        <v>1805</v>
+        <v>1803</v>
       </c>
       <c r="C29" s="3" t="s">
+        <v>66</v>
+      </c>
+      <c r="D29" s="4" t="s">
         <v>64</v>
       </c>
-      <c r="D29" s="4" t="s">
-        <v>60</v>
-      </c>
       <c r="E29" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F29" s="3" t="s">
-        <v>64</v>
+        <v>66</v>
       </c>
     </row>
     <row r="30" ht="16.5" customHeight="1" spans="1:6">
       <c r="A30" s="3"/>
       <c r="B30" s="3">
-        <v>1806</v>
+        <v>1804</v>
       </c>
       <c r="C30" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
       <c r="D30" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E30" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F30" s="3" t="s">
-        <v>65</v>
+        <v>67</v>
       </c>
     </row>
     <row r="31" ht="16.5" customHeight="1" spans="1:6">
       <c r="A31" s="3"/>
       <c r="B31" s="3">
-        <v>1807</v>
+        <v>1805</v>
       </c>
       <c r="C31" s="3" t="s">
-        <v>66</v>
+        <v>68</v>
       </c>
       <c r="D31" s="4" t="s">
-        <v>60</v>
+        <v>64</v>
       </c>
       <c r="E31" s="3" t="s">
-        <v>40</v>
+        <v>44</v>
       </c>
       <c r="F31" s="3" t="s">
-        <v>66</v>
-      </c>
-    </row>
-    <row r="32" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
+        <v>68</v>
+      </c>
+    </row>
+    <row r="32" ht="16.5" customHeight="1" spans="1:6">
       <c r="A32" s="3"/>
       <c r="B32" s="3">
-        <v>2001</v>
+        <v>1806</v>
       </c>
       <c r="C32" s="3" t="s">
-        <v>67</v>
-      </c>
-      <c r="D32" s="3" t="s">
-        <v>68</v>
+        <v>69</v>
+      </c>
+      <c r="D32" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="E32" s="3" t="s">
+        <v>44</v>
+      </c>
+      <c r="F32" s="3" t="s">
         <v>69</v>
-      </c>
-      <c r="F32" s="3" t="s">
-        <v>67</v>
       </c>
     </row>
     <row r="33" ht="16.5" customHeight="1" spans="1:6">
       <c r="A33" s="3"/>
       <c r="B33" s="3">
-        <v>2002</v>
+        <v>1807</v>
       </c>
       <c r="C33" s="3" t="s">
         <v>70</v>
       </c>
-      <c r="D33" s="3" t="s">
-        <v>71</v>
+      <c r="D33" s="4" t="s">
+        <v>64</v>
       </c>
       <c r="E33" s="3" t="s">
-        <v>69</v>
+        <v>44</v>
       </c>
       <c r="F33" s="3" t="s">
         <v>70</v>
       </c>
     </row>
-    <row r="34" ht="16.5" customHeight="1" spans="1:6">
+    <row r="34" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A34" s="3"/>
       <c r="B34" s="3">
-        <v>2003</v>
+        <v>2001</v>
       </c>
       <c r="C34" s="3" t="s">
+        <v>71</v>
+      </c>
+      <c r="D34" s="3" t="s">
         <v>72</v>
       </c>
-      <c r="D34" s="3" t="s">
+      <c r="E34" s="3" t="s">
         <v>73</v>
       </c>
-      <c r="E34" s="3" t="s">
-        <v>69</v>
-      </c>
       <c r="F34" s="3" t="s">
-        <v>72</v>
+        <v>71</v>
       </c>
     </row>
     <row r="35" ht="16.5" customHeight="1" spans="1:6">
       <c r="A35" s="3"/>
       <c r="B35" s="3">
-        <v>2004</v>
+        <v>2002</v>
       </c>
       <c r="C35" s="3" t="s">
         <v>74</v>
@@ -2468,7 +2486,7 @@
         <v>75</v>
       </c>
       <c r="E35" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F35" s="3" t="s">
         <v>74</v>
@@ -2477,7 +2495,7 @@
     <row r="36" ht="16.5" customHeight="1" spans="1:6">
       <c r="A36" s="3"/>
       <c r="B36" s="3">
-        <v>2005</v>
+        <v>2003</v>
       </c>
       <c r="C36" s="3" t="s">
         <v>76</v>
@@ -2486,7 +2504,7 @@
         <v>77</v>
       </c>
       <c r="E36" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F36" s="3" t="s">
         <v>76</v>
@@ -2495,7 +2513,7 @@
     <row r="37" ht="16.5" customHeight="1" spans="1:6">
       <c r="A37" s="3"/>
       <c r="B37" s="3">
-        <v>2006</v>
+        <v>2004</v>
       </c>
       <c r="C37" s="3" t="s">
         <v>78</v>
@@ -2504,7 +2522,7 @@
         <v>79</v>
       </c>
       <c r="E37" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F37" s="3" t="s">
         <v>78</v>
@@ -2513,7 +2531,7 @@
     <row r="38" ht="16.5" customHeight="1" spans="1:6">
       <c r="A38" s="3"/>
       <c r="B38" s="3">
-        <v>2007</v>
+        <v>2005</v>
       </c>
       <c r="C38" s="3" t="s">
         <v>80</v>
@@ -2522,7 +2540,7 @@
         <v>81</v>
       </c>
       <c r="E38" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F38" s="3" t="s">
         <v>80</v>
@@ -2531,7 +2549,7 @@
     <row r="39" ht="16.5" customHeight="1" spans="1:6">
       <c r="A39" s="3"/>
       <c r="B39" s="3">
-        <v>2008</v>
+        <v>2006</v>
       </c>
       <c r="C39" s="3" t="s">
         <v>82</v>
@@ -2540,7 +2558,7 @@
         <v>83</v>
       </c>
       <c r="E39" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F39" s="3" t="s">
         <v>82</v>
@@ -2549,7 +2567,7 @@
     <row r="40" ht="16.5" customHeight="1" spans="1:6">
       <c r="A40" s="3"/>
       <c r="B40" s="3">
-        <v>2009</v>
+        <v>2007</v>
       </c>
       <c r="C40" s="3" t="s">
         <v>84</v>
@@ -2558,7 +2576,7 @@
         <v>85</v>
       </c>
       <c r="E40" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F40" s="3" t="s">
         <v>84</v>
@@ -2567,7 +2585,7 @@
     <row r="41" ht="16.5" customHeight="1" spans="1:6">
       <c r="A41" s="3"/>
       <c r="B41" s="3">
-        <v>2010</v>
+        <v>2008</v>
       </c>
       <c r="C41" s="3" t="s">
         <v>86</v>
@@ -2576,7 +2594,7 @@
         <v>87</v>
       </c>
       <c r="E41" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F41" s="3" t="s">
         <v>86</v>
@@ -2585,7 +2603,7 @@
     <row r="42" ht="16.5" customHeight="1" spans="1:6">
       <c r="A42" s="3"/>
       <c r="B42" s="3">
-        <v>2011</v>
+        <v>2009</v>
       </c>
       <c r="C42" s="3" t="s">
         <v>88</v>
@@ -2594,7 +2612,7 @@
         <v>89</v>
       </c>
       <c r="E42" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F42" s="3" t="s">
         <v>88</v>
@@ -2603,7 +2621,7 @@
     <row r="43" ht="16.5" customHeight="1" spans="1:6">
       <c r="A43" s="3"/>
       <c r="B43" s="3">
-        <v>2012</v>
+        <v>2010</v>
       </c>
       <c r="C43" s="3" t="s">
         <v>90</v>
@@ -2612,7 +2630,7 @@
         <v>91</v>
       </c>
       <c r="E43" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F43" s="3" t="s">
         <v>90</v>
@@ -2621,7 +2639,7 @@
     <row r="44" ht="16.5" customHeight="1" spans="1:6">
       <c r="A44" s="3"/>
       <c r="B44" s="3">
-        <v>2013</v>
+        <v>2011</v>
       </c>
       <c r="C44" s="3" t="s">
         <v>92</v>
@@ -2630,7 +2648,7 @@
         <v>93</v>
       </c>
       <c r="E44" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F44" s="3" t="s">
         <v>92</v>
@@ -2639,7 +2657,7 @@
     <row r="45" ht="16.5" customHeight="1" spans="1:6">
       <c r="A45" s="3"/>
       <c r="B45" s="3">
-        <v>2014</v>
+        <v>2012</v>
       </c>
       <c r="C45" s="3" t="s">
         <v>94</v>
@@ -2648,7 +2666,7 @@
         <v>95</v>
       </c>
       <c r="E45" s="3" t="s">
-        <v>69</v>
+        <v>73</v>
       </c>
       <c r="F45" s="3" t="s">
         <v>94</v>
@@ -2657,7 +2675,7 @@
     <row r="46" ht="16.5" customHeight="1" spans="1:6">
       <c r="A46" s="3"/>
       <c r="B46" s="3">
-        <v>5001</v>
+        <v>2013</v>
       </c>
       <c r="C46" s="3" t="s">
         <v>96</v>
@@ -2666,7 +2684,7 @@
         <v>97</v>
       </c>
       <c r="E46" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F46" s="3" t="s">
         <v>96</v>
@@ -2675,61 +2693,61 @@
     <row r="47" ht="16.5" customHeight="1" spans="1:6">
       <c r="A47" s="3"/>
       <c r="B47" s="3">
-        <v>5002</v>
+        <v>2014</v>
       </c>
       <c r="C47" s="3" t="s">
+        <v>98</v>
+      </c>
+      <c r="D47" s="3" t="s">
         <v>99</v>
       </c>
-      <c r="D47" s="3" t="s">
-        <v>100</v>
-      </c>
       <c r="E47" s="3" t="s">
+        <v>73</v>
+      </c>
+      <c r="F47" s="3" t="s">
         <v>98</v>
       </c>
-      <c r="F47" s="3" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="48" ht="16.5" customHeight="1" spans="1:6">
+    </row>
+    <row r="48" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A48" s="3"/>
       <c r="B48" s="3">
-        <v>5003</v>
+        <v>2015</v>
       </c>
       <c r="C48" s="3" t="s">
+        <v>100</v>
+      </c>
+      <c r="D48" s="3" t="s">
         <v>101</v>
       </c>
-      <c r="D48" s="3" t="s">
-        <v>102</v>
-      </c>
       <c r="E48" s="3" t="s">
-        <v>98</v>
+        <v>73</v>
       </c>
       <c r="F48" s="3" t="s">
-        <v>101</v>
+        <v>100</v>
       </c>
     </row>
     <row r="49" ht="16.5" customHeight="1" spans="1:6">
       <c r="A49" s="3"/>
       <c r="B49" s="3">
-        <v>5101</v>
+        <v>5001</v>
       </c>
       <c r="C49" s="3" t="s">
+        <v>102</v>
+      </c>
+      <c r="D49" s="3" t="s">
         <v>103</v>
       </c>
-      <c r="D49" s="3" t="s">
+      <c r="E49" s="3" t="s">
         <v>104</v>
       </c>
-      <c r="E49" s="3" t="s">
-        <v>98</v>
-      </c>
       <c r="F49" s="3" t="s">
-        <v>103</v>
+        <v>102</v>
       </c>
     </row>
     <row r="50" ht="16.5" customHeight="1" spans="1:6">
       <c r="A50" s="3"/>
       <c r="B50" s="3">
-        <v>5102</v>
+        <v>5002</v>
       </c>
       <c r="C50" s="3" t="s">
         <v>105</v>
@@ -2738,7 +2756,7 @@
         <v>106</v>
       </c>
       <c r="E50" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F50" s="3" t="s">
         <v>105</v>
@@ -2747,7 +2765,7 @@
     <row r="51" ht="16.5" customHeight="1" spans="1:6">
       <c r="A51" s="3"/>
       <c r="B51" s="3">
-        <v>5103</v>
+        <v>5003</v>
       </c>
       <c r="C51" s="3" t="s">
         <v>107</v>
@@ -2756,7 +2774,7 @@
         <v>108</v>
       </c>
       <c r="E51" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F51" s="3" t="s">
         <v>107</v>
@@ -2765,7 +2783,7 @@
     <row r="52" ht="16.5" customHeight="1" spans="1:6">
       <c r="A52" s="3"/>
       <c r="B52" s="3">
-        <v>5104</v>
+        <v>5101</v>
       </c>
       <c r="C52" s="3" t="s">
         <v>109</v>
@@ -2774,7 +2792,7 @@
         <v>110</v>
       </c>
       <c r="E52" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F52" s="3" t="s">
         <v>109</v>
@@ -2783,7 +2801,7 @@
     <row r="53" ht="16.5" customHeight="1" spans="1:6">
       <c r="A53" s="3"/>
       <c r="B53" s="3">
-        <v>5105</v>
+        <v>5102</v>
       </c>
       <c r="C53" s="3" t="s">
         <v>111</v>
@@ -2792,7 +2810,7 @@
         <v>112</v>
       </c>
       <c r="E53" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F53" s="3" t="s">
         <v>111</v>
@@ -2801,7 +2819,7 @@
     <row r="54" ht="16.5" customHeight="1" spans="1:6">
       <c r="A54" s="3"/>
       <c r="B54" s="3">
-        <v>5106</v>
+        <v>5103</v>
       </c>
       <c r="C54" s="3" t="s">
         <v>113</v>
@@ -2810,7 +2828,7 @@
         <v>114</v>
       </c>
       <c r="E54" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F54" s="3" t="s">
         <v>113</v>
@@ -2819,7 +2837,7 @@
     <row r="55" ht="16.5" customHeight="1" spans="1:6">
       <c r="A55" s="3"/>
       <c r="B55" s="3">
-        <v>5107</v>
+        <v>5104</v>
       </c>
       <c r="C55" s="3" t="s">
         <v>115</v>
@@ -2828,7 +2846,7 @@
         <v>116</v>
       </c>
       <c r="E55" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F55" s="3" t="s">
         <v>115</v>
@@ -2837,7 +2855,7 @@
     <row r="56" ht="16.5" customHeight="1" spans="1:6">
       <c r="A56" s="3"/>
       <c r="B56" s="3">
-        <v>5201</v>
+        <v>5105</v>
       </c>
       <c r="C56" s="3" t="s">
         <v>117</v>
@@ -2846,7 +2864,7 @@
         <v>118</v>
       </c>
       <c r="E56" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F56" s="3" t="s">
         <v>117</v>
@@ -2855,7 +2873,7 @@
     <row r="57" ht="16.5" customHeight="1" spans="1:6">
       <c r="A57" s="3"/>
       <c r="B57" s="3">
-        <v>5202</v>
+        <v>5106</v>
       </c>
       <c r="C57" s="3" t="s">
         <v>119</v>
@@ -2864,7 +2882,7 @@
         <v>120</v>
       </c>
       <c r="E57" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F57" s="3" t="s">
         <v>119</v>
@@ -2873,7 +2891,7 @@
     <row r="58" ht="16.5" customHeight="1" spans="1:6">
       <c r="A58" s="3"/>
       <c r="B58" s="3">
-        <v>5301</v>
+        <v>5107</v>
       </c>
       <c r="C58" s="3" t="s">
         <v>121</v>
@@ -2882,7 +2900,7 @@
         <v>122</v>
       </c>
       <c r="E58" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F58" s="3" t="s">
         <v>121</v>
@@ -2891,7 +2909,7 @@
     <row r="59" ht="16.5" customHeight="1" spans="1:6">
       <c r="A59" s="3"/>
       <c r="B59" s="3">
-        <v>5302</v>
+        <v>5201</v>
       </c>
       <c r="C59" s="3" t="s">
         <v>123</v>
@@ -2900,7 +2918,7 @@
         <v>124</v>
       </c>
       <c r="E59" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F59" s="3" t="s">
         <v>123</v>
@@ -2909,7 +2927,7 @@
     <row r="60" ht="16.5" customHeight="1" spans="1:6">
       <c r="A60" s="3"/>
       <c r="B60" s="3">
-        <v>5528</v>
+        <v>5202</v>
       </c>
       <c r="C60" s="3" t="s">
         <v>125</v>
@@ -2918,7 +2936,7 @@
         <v>126</v>
       </c>
       <c r="E60" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F60" s="3" t="s">
         <v>125</v>
@@ -2927,7 +2945,7 @@
     <row r="61" ht="16.5" customHeight="1" spans="1:6">
       <c r="A61" s="3"/>
       <c r="B61" s="3">
-        <v>5529</v>
+        <v>5301</v>
       </c>
       <c r="C61" s="3" t="s">
         <v>127</v>
@@ -2936,7 +2954,7 @@
         <v>128</v>
       </c>
       <c r="E61" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F61" s="3" t="s">
         <v>127</v>
@@ -2945,7 +2963,7 @@
     <row r="62" ht="16.5" customHeight="1" spans="1:6">
       <c r="A62" s="3"/>
       <c r="B62" s="3">
-        <v>5530</v>
+        <v>5302</v>
       </c>
       <c r="C62" s="3" t="s">
         <v>129</v>
@@ -2954,7 +2972,7 @@
         <v>130</v>
       </c>
       <c r="E62" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F62" s="3" t="s">
         <v>129</v>
@@ -2963,7 +2981,7 @@
     <row r="63" ht="16.5" customHeight="1" spans="1:6">
       <c r="A63" s="3"/>
       <c r="B63" s="3">
-        <v>5531</v>
+        <v>5528</v>
       </c>
       <c r="C63" s="3" t="s">
         <v>131</v>
@@ -2972,7 +2990,7 @@
         <v>132</v>
       </c>
       <c r="E63" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F63" s="3" t="s">
         <v>131</v>
@@ -2981,7 +2999,7 @@
     <row r="64" ht="16.5" customHeight="1" spans="1:6">
       <c r="A64" s="3"/>
       <c r="B64" s="3">
-        <v>5532</v>
+        <v>5529</v>
       </c>
       <c r="C64" s="3" t="s">
         <v>133</v>
@@ -2990,7 +3008,7 @@
         <v>134</v>
       </c>
       <c r="E64" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F64" s="3" t="s">
         <v>133</v>
@@ -2999,7 +3017,7 @@
     <row r="65" ht="16.5" customHeight="1" spans="1:6">
       <c r="A65" s="3"/>
       <c r="B65" s="3">
-        <v>5533</v>
+        <v>5530</v>
       </c>
       <c r="C65" s="3" t="s">
         <v>135</v>
@@ -3008,7 +3026,7 @@
         <v>136</v>
       </c>
       <c r="E65" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F65" s="3" t="s">
         <v>135</v>
@@ -3017,7 +3035,7 @@
     <row r="66" ht="16.5" customHeight="1" spans="1:6">
       <c r="A66" s="3"/>
       <c r="B66" s="3">
-        <v>5534</v>
+        <v>5531</v>
       </c>
       <c r="C66" s="3" t="s">
         <v>137</v>
@@ -3026,7 +3044,7 @@
         <v>138</v>
       </c>
       <c r="E66" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F66" s="3" t="s">
         <v>137</v>
@@ -3035,7 +3053,7 @@
     <row r="67" ht="16.5" customHeight="1" spans="1:6">
       <c r="A67" s="3"/>
       <c r="B67" s="3">
-        <v>5535</v>
+        <v>5532</v>
       </c>
       <c r="C67" s="3" t="s">
         <v>139</v>
@@ -3044,7 +3062,7 @@
         <v>140</v>
       </c>
       <c r="E67" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F67" s="3" t="s">
         <v>139</v>
@@ -3053,7 +3071,7 @@
     <row r="68" ht="16.5" customHeight="1" spans="1:6">
       <c r="A68" s="3"/>
       <c r="B68" s="3">
-        <v>5536</v>
+        <v>5533</v>
       </c>
       <c r="C68" s="3" t="s">
         <v>141</v>
@@ -3062,7 +3080,7 @@
         <v>142</v>
       </c>
       <c r="E68" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F68" s="3" t="s">
         <v>141</v>
@@ -3071,7 +3089,7 @@
     <row r="69" ht="16.5" customHeight="1" spans="1:6">
       <c r="A69" s="3"/>
       <c r="B69" s="3">
-        <v>5537</v>
+        <v>5534</v>
       </c>
       <c r="C69" s="3" t="s">
         <v>143</v>
@@ -3080,7 +3098,7 @@
         <v>144</v>
       </c>
       <c r="E69" s="3" t="s">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="F69" s="3" t="s">
         <v>143</v>
@@ -3089,7 +3107,7 @@
     <row r="70" ht="16.5" customHeight="1" spans="1:6">
       <c r="A70" s="3"/>
       <c r="B70" s="3">
-        <v>10001</v>
+        <v>5535</v>
       </c>
       <c r="C70" s="3" t="s">
         <v>145</v>
@@ -3098,162 +3116,162 @@
         <v>146</v>
       </c>
       <c r="E70" s="3" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="F70" s="3" t="s">
-        <v>148</v>
+        <v>145</v>
       </c>
     </row>
     <row r="71" ht="16.5" customHeight="1" spans="1:6">
       <c r="A71" s="3"/>
       <c r="B71" s="3">
-        <v>10002</v>
+        <v>5536</v>
       </c>
       <c r="C71" s="3" t="s">
-        <v>149</v>
+        <v>147</v>
       </c>
       <c r="D71" s="3" t="s">
-        <v>150</v>
+        <v>148</v>
       </c>
       <c r="E71" s="3" t="s">
+        <v>104</v>
+      </c>
+      <c r="F71" s="3" t="s">
         <v>147</v>
-      </c>
-      <c r="F71" s="3" t="s">
-        <v>151</v>
       </c>
     </row>
     <row r="72" ht="16.5" customHeight="1" spans="1:6">
       <c r="A72" s="3"/>
       <c r="B72" s="3">
-        <v>10003</v>
+        <v>5537</v>
       </c>
       <c r="C72" s="3" t="s">
-        <v>152</v>
+        <v>149</v>
       </c>
       <c r="D72" s="3" t="s">
-        <v>153</v>
+        <v>150</v>
       </c>
       <c r="E72" s="3" t="s">
-        <v>147</v>
+        <v>104</v>
       </c>
       <c r="F72" s="3" t="s">
-        <v>154</v>
+        <v>149</v>
       </c>
     </row>
     <row r="73" ht="16.5" customHeight="1" spans="1:6">
       <c r="A73" s="3"/>
       <c r="B73" s="3">
-        <v>10004</v>
+        <v>10001</v>
       </c>
       <c r="C73" s="3" t="s">
-        <v>155</v>
+        <v>151</v>
       </c>
       <c r="D73" s="3" t="s">
-        <v>156</v>
+        <v>152</v>
       </c>
       <c r="E73" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F73" s="3" t="s">
-        <v>157</v>
+        <v>154</v>
       </c>
     </row>
     <row r="74" ht="16.5" customHeight="1" spans="1:6">
       <c r="A74" s="3"/>
       <c r="B74" s="3">
-        <v>10005</v>
+        <v>10002</v>
       </c>
       <c r="C74" s="3" t="s">
+        <v>155</v>
+      </c>
+      <c r="D74" s="3" t="s">
+        <v>156</v>
+      </c>
+      <c r="E74" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F74" s="3" t="s">
+        <v>157</v>
+      </c>
+    </row>
+    <row r="75" ht="16.5" customHeight="1" spans="1:6">
+      <c r="A75" s="3"/>
+      <c r="B75" s="3">
+        <v>10003</v>
+      </c>
+      <c r="C75" s="3" t="s">
         <v>158</v>
       </c>
-      <c r="D74" s="3" t="s">
+      <c r="D75" s="3" t="s">
         <v>159</v>
       </c>
-      <c r="E74" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F74" s="3" t="s">
+      <c r="E75" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F75" s="3" t="s">
         <v>160</v>
       </c>
     </row>
-    <row r="75" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A75" s="3" t="s">
-        <v>3</v>
-      </c>
-      <c r="B75" s="3">
-        <v>12001</v>
-      </c>
-      <c r="C75" s="3" t="s">
-        <v>161</v>
-      </c>
-      <c r="D75" s="3" t="s">
-        <v>162</v>
-      </c>
-      <c r="E75" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F75" s="3" t="s">
-        <v>163</v>
-      </c>
-    </row>
-    <row r="76" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
+    <row r="76" ht="16.5" customHeight="1" spans="1:6">
       <c r="A76" s="3"/>
       <c r="B76" s="3">
-        <v>12001</v>
+        <v>10004</v>
       </c>
       <c r="C76" s="3" t="s">
-        <v>164</v>
+        <v>161</v>
       </c>
       <c r="D76" s="3" t="s">
-        <v>165</v>
+        <v>162</v>
       </c>
       <c r="E76" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F76" s="3" t="s">
-        <v>164</v>
-      </c>
-    </row>
-    <row r="77" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
+        <v>163</v>
+      </c>
+    </row>
+    <row r="77" ht="16.5" customHeight="1" spans="1:6">
       <c r="A77" s="3"/>
       <c r="B77" s="3">
-        <v>12002</v>
+        <v>10005</v>
       </c>
       <c r="C77" s="3" t="s">
-        <v>166</v>
+        <v>164</v>
       </c>
       <c r="D77" s="3" t="s">
-        <v>167</v>
+        <v>165</v>
       </c>
       <c r="E77" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F77" s="3" t="s">
         <v>166</v>
       </c>
     </row>
-    <row r="78" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
-      <c r="A78" s="3"/>
+    <row r="78" ht="16.5" customHeight="1" spans="1:6">
+      <c r="A78" s="3" t="s">
+        <v>3</v>
+      </c>
       <c r="B78" s="3">
-        <v>12003</v>
+        <v>12001</v>
       </c>
       <c r="C78" s="3" t="s">
+        <v>167</v>
+      </c>
+      <c r="D78" s="3" t="s">
         <v>168</v>
       </c>
-      <c r="D78" s="3" t="s">
+      <c r="E78" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F78" s="3" t="s">
         <v>169</v>
-      </c>
-      <c r="E78" s="3" t="s">
-        <v>147</v>
-      </c>
-      <c r="F78" s="3" t="s">
-        <v>168</v>
       </c>
     </row>
     <row r="79" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A79" s="3"/>
       <c r="B79" s="3">
-        <v>12004</v>
+        <v>12001</v>
       </c>
       <c r="C79" s="3" t="s">
         <v>170</v>
@@ -3262,7 +3280,7 @@
         <v>171</v>
       </c>
       <c r="E79" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F79" s="3" t="s">
         <v>170</v>
@@ -3271,7 +3289,7 @@
     <row r="80" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A80" s="3"/>
       <c r="B80" s="3">
-        <v>12005</v>
+        <v>12002</v>
       </c>
       <c r="C80" s="3" t="s">
         <v>172</v>
@@ -3280,7 +3298,7 @@
         <v>173</v>
       </c>
       <c r="E80" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F80" s="3" t="s">
         <v>172</v>
@@ -3289,7 +3307,7 @@
     <row r="81" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A81" s="3"/>
       <c r="B81" s="3">
-        <v>12006</v>
+        <v>12003</v>
       </c>
       <c r="C81" s="3" t="s">
         <v>174</v>
@@ -3298,7 +3316,7 @@
         <v>175</v>
       </c>
       <c r="E81" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F81" s="3" t="s">
         <v>174</v>
@@ -3307,7 +3325,7 @@
     <row r="82" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A82" s="3"/>
       <c r="B82" s="3">
-        <v>12007</v>
+        <v>12004</v>
       </c>
       <c r="C82" s="3" t="s">
         <v>176</v>
@@ -3316,7 +3334,7 @@
         <v>177</v>
       </c>
       <c r="E82" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F82" s="3" t="s">
         <v>176</v>
@@ -3325,7 +3343,7 @@
     <row r="83" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A83" s="3"/>
       <c r="B83" s="3">
-        <v>12008</v>
+        <v>12005</v>
       </c>
       <c r="C83" s="3" t="s">
         <v>178</v>
@@ -3334,16 +3352,16 @@
         <v>179</v>
       </c>
       <c r="E83" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F83" s="3" t="s">
         <v>178</v>
       </c>
     </row>
-    <row r="84" customFormat="1" ht="16.5" spans="1:6">
+    <row r="84" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A84" s="3"/>
       <c r="B84" s="3">
-        <v>13001</v>
+        <v>12006</v>
       </c>
       <c r="C84" s="3" t="s">
         <v>180</v>
@@ -3352,16 +3370,16 @@
         <v>181</v>
       </c>
       <c r="E84" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F84" s="3" t="s">
         <v>180</v>
       </c>
     </row>
-    <row r="85" customFormat="1" ht="16.5" spans="1:6">
+    <row r="85" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
       <c r="A85" s="3"/>
       <c r="B85" s="3">
-        <v>13002</v>
+        <v>12007</v>
       </c>
       <c r="C85" s="3" t="s">
         <v>182</v>
@@ -3370,151 +3388,222 @@
         <v>183</v>
       </c>
       <c r="E85" s="3" t="s">
-        <v>147</v>
+        <v>153</v>
       </c>
       <c r="F85" s="3" t="s">
         <v>182</v>
       </c>
     </row>
+    <row r="86" customFormat="1" ht="16.5" customHeight="1" spans="1:6">
+      <c r="A86" s="3"/>
+      <c r="B86" s="3">
+        <v>12008</v>
+      </c>
+      <c r="C86" s="3" t="s">
+        <v>184</v>
+      </c>
+      <c r="D86" s="3" t="s">
+        <v>185</v>
+      </c>
+      <c r="E86" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F86" s="3" t="s">
+        <v>184</v>
+      </c>
+    </row>
+    <row r="87" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A87" s="3"/>
+      <c r="B87" s="3">
+        <v>13001</v>
+      </c>
+      <c r="C87" s="3" t="s">
+        <v>186</v>
+      </c>
+      <c r="D87" s="3" t="s">
+        <v>187</v>
+      </c>
+      <c r="E87" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F87" s="3" t="s">
+        <v>186</v>
+      </c>
+    </row>
+    <row r="88" customFormat="1" ht="16.5" spans="1:6">
+      <c r="A88" s="3"/>
+      <c r="B88" s="3">
+        <v>13002</v>
+      </c>
+      <c r="C88" s="3" t="s">
+        <v>188</v>
+      </c>
+      <c r="D88" s="3" t="s">
+        <v>189</v>
+      </c>
+      <c r="E88" s="3" t="s">
+        <v>153</v>
+      </c>
+      <c r="F88" s="3" t="s">
+        <v>188</v>
+      </c>
+    </row>
   </sheetData>
   <conditionalFormatting sqref="E4">
-    <cfRule type="cellIs" dxfId="0" priority="15" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="14" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="13" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="12" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="11" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E10">
-    <cfRule type="cellIs" dxfId="0" priority="45" operator="equal">
+  <conditionalFormatting sqref="E34">
+    <cfRule type="cellIs" dxfId="4" priority="6" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="7" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="8" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="9" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="10" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="40" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E48">
+    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="35" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="30" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="25" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E32">
     <cfRule type="cellIs" dxfId="0" priority="5" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="4" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E79">
+    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="134" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="3" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="2" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="1" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E76">
-    <cfRule type="cellIs" dxfId="4" priority="126" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="127" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="128" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="129" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="130" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="135" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
   <conditionalFormatting sqref="E5:E9">
-    <cfRule type="cellIs" dxfId="4" priority="46" operator="equal">
+    <cfRule type="cellIs" dxfId="4" priority="51" operator="equal">
       <formula>"其他"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="47" operator="equal">
+    <cfRule type="cellIs" dxfId="3" priority="52" operator="equal">
       <formula>"爆炸"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="48" operator="equal">
+    <cfRule type="cellIs" dxfId="2" priority="53" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="49" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="54" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="55" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E10:E12">
+    <cfRule type="cellIs" dxfId="4" priority="30" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="35" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="40" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="45" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
     <cfRule type="cellIs" dxfId="0" priority="50" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
-  <conditionalFormatting sqref="E11:E14">
-    <cfRule type="cellIs" dxfId="0" priority="20" operator="equal">
+  <conditionalFormatting sqref="E13:E16">
+    <cfRule type="cellIs" dxfId="4" priority="21" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="22" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="23" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="24" operator="equal">
+      <formula>"子弹发射"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="0" priority="25" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="19" operator="equal">
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E80:E88">
+    <cfRule type="cellIs" dxfId="4" priority="91" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="92" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="93" operator="equal">
+      <formula>"子弹"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="1" priority="94" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="18" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="95" operator="equal">
+      <formula>"子弹命中"</formula>
+    </cfRule>
+  </conditionalFormatting>
+  <conditionalFormatting sqref="E17:E33 E89:E1048576 E49:E78 E35:E47">
+    <cfRule type="cellIs" dxfId="4" priority="136" operator="equal">
+      <formula>"其他"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="3" priority="137" operator="equal">
+      <formula>"爆炸"</formula>
+    </cfRule>
+    <cfRule type="cellIs" dxfId="2" priority="138" operator="equal">
       <formula>"子弹"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="17" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="4" priority="16" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E77:E85">
-    <cfRule type="cellIs" dxfId="4" priority="86" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="87" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="88" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="89" operator="equal">
+    <cfRule type="cellIs" dxfId="1" priority="139" operator="equal">
       <formula>"子弹发射"</formula>
     </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="90" operator="equal">
-      <formula>"子弹命中"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <conditionalFormatting sqref="E15:E31 E33:E75 E86:E1048576">
-    <cfRule type="cellIs" dxfId="4" priority="131" operator="equal">
-      <formula>"其他"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="3" priority="132" operator="equal">
-      <formula>"爆炸"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="2" priority="133" operator="equal">
-      <formula>"子弹"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="1" priority="134" operator="equal">
-      <formula>"子弹发射"</formula>
-    </cfRule>
-    <cfRule type="cellIs" dxfId="0" priority="135" operator="equal">
+    <cfRule type="cellIs" dxfId="0" priority="140" operator="equal">
       <formula>"子弹命中"</formula>
     </cfRule>
   </conditionalFormatting>
   <dataValidations count="1">
-    <dataValidation type="list" sqref="E4:E1048576">
+    <dataValidation type="list" sqref="E48 E4:E9 E10:E12 E13:E47 E49:E1048576">
       <formula1>"其他,子弹发射,子弹,子弹命中,爆炸"</formula1>
     </dataValidation>
   </dataValidations>
